--- a/InputData/elec/BEVGB/BAU EV Grid Balancing.xlsx
+++ b/InputData/elec/BEVGB/BAU EV Grid Balancing.xlsx
@@ -1,57 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BEVGB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\elec\BEVGB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D093AAE9-7352-40DE-876A-6770C14DDEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BC45A4-E2C4-46AA-BE53-07018726AC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6450" yWindow="2820" windowWidth="29460" windowHeight="20220" xr2:uid="{655D3588-F202-41C7-8FE2-794AD3DDEF83}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BEVGB-fraction-of-EVs" sheetId="2" r:id="rId2"/>
     <sheet name="BEVGB-fraction-of-bat-cap" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>BEVGB BAU Electric Vehicle Grid Balancing Fraction of EVs Used for Grid Balancing on Average Day</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
     <t>BEVGB BAU Electric Vehicle Grid Balancing Fraction of EV Battery Capacity Used for Grid Balancing when EV is Used for Grid Balancing</t>
   </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Unit: dimensionless (fraction of EVs)</t>
+  </si>
+  <si>
+    <t>Fraction of EVs used for grid balancing on an average day</t>
+  </si>
+  <si>
+    <t>Fraction of battery capacity used for grid balancing when EV is used for grid balancing</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (fraction of battery capacity)</t>
+  </si>
+  <si>
+    <t>Fraction of capacity</t>
+  </si>
+  <si>
     <t>assuming no use of EVs for grid balancing in BAU case</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (fraction of EVs)</t>
-  </si>
-  <si>
-    <t>Fraction of EVs used for grid balancing on an average day</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (fraction of battery capacity)</t>
-  </si>
-  <si>
-    <t>Fraction of capacity</t>
-  </si>
-  <si>
-    <t>Fraction of battery capacity used for grid balancing when EV is used for grid balancing</t>
   </si>
 </sst>
 </file>
@@ -428,7 +441,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5907010-7D78-42B4-8F29-C2B746359EDF}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -436,21 +449,18 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -459,7 +469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D5529C-47BA-4DC5-A906-F6DA44067A58}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -469,9 +479,9 @@
     <col min="1" max="1" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -564,9 +574,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -665,7 +675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6678A088-8860-4D31-B0C3-9CFD56EB5FDB}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -676,17 +686,17 @@
     <col min="2" max="2" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0.25</v>
